--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomok\OneDrive\デスクトップ\WebAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomok\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A284A32-3F1A-49C0-84F1-37FE77625D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18107001-3A5F-4115-B388-69D795751064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="178">
   <si>
     <t>参加</t>
   </si>
@@ -552,13 +552,62 @@
   </si>
   <si>
     <t>指</t>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>まいぴ</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ゆうか</t>
+    </r>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,6 +659,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -763,14 +818,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1847,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.59765625" style="6" customWidth="1"/>
@@ -1889,7 +1944,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>30</v>
@@ -1906,55 +1961,53 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>30</v>
@@ -1969,13 +2022,13 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3">
-        <v>4</v>
+      <c r="D6" s="6">
+        <v>3.5</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>30</v>
@@ -1987,15 +2040,15 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="6">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -2008,217 +2061,205 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F9"/>
       <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10"/>
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="6">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.5</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="6">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.5</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="6">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
-        <v>30</v>
+      <c r="A15" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="6">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F15"/>
       <c r="G15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.5</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
+      <c r="A17" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D17" s="6">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>30</v>
@@ -2230,37 +2271,37 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="3"/>
-      <c r="B19" s="18" t="s">
-        <v>31</v>
+      <c r="A19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>30</v>
@@ -2273,7 +2314,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="3"/>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>15</v>
@@ -2292,12 +2333,12 @@
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="3"/>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="6">
         <v>4</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -2311,7 +2352,7 @@
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="3"/>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
@@ -2319,29 +2360,27 @@
       <c r="D22" s="3">
         <v>4</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="3"/>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="3">
         <v>4</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F23"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>30</v>
       </c>
@@ -2349,18 +2388,20 @@
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="3"/>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="3">
         <v>4</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>30</v>
       </c>
@@ -2368,10 +2409,10 @@
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="3"/>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" s="3">
         <v>4</v>
@@ -2379,7 +2420,9 @@
       <c r="E25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>30</v>
       </c>
@@ -2387,18 +2430,20 @@
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="3"/>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="6">
         <v>4</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G26" s="3" t="s">
         <v>30</v>
       </c>
@@ -2406,18 +2451,20 @@
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="3"/>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="6">
         <v>4</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G27" s="3" t="s">
         <v>30</v>
       </c>
@@ -2425,12 +2472,12 @@
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="3"/>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="6">
         <v>4</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -2446,12 +2493,12 @@
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="3"/>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="3">
+        <v>11</v>
+      </c>
+      <c r="D29" s="6">
         <v>4</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -2467,18 +2514,18 @@
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="3"/>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="6">
         <v>4</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30"/>
       <c r="G30" s="3" t="s">
         <v>30</v>
       </c>
@@ -2486,7 +2533,7 @@
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="3"/>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>11</v>
@@ -2497,18 +2544,20 @@
       <c r="E31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G31" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="3"/>
-      <c r="B32" t="s">
-        <v>44</v>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3">
         <v>4</v>
@@ -2524,10 +2573,10 @@
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="3"/>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D33" s="3">
         <v>4</v>
@@ -2543,7 +2592,7 @@
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="3"/>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2562,7 +2611,7 @@
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="3"/>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>11</v>
@@ -2573,9 +2622,7 @@
       <c r="E35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>30</v>
       </c>
@@ -2583,18 +2630,18 @@
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="3"/>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="3">
+        <v>11</v>
+      </c>
+      <c r="D36" s="6">
         <v>4</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36"/>
       <c r="G36" s="3" t="s">
         <v>30</v>
       </c>
@@ -2602,12 +2649,12 @@
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="3"/>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="6">
         <v>4</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -2621,10 +2668,10 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="3"/>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D38" s="3">
         <v>4</v>
@@ -2640,7 +2687,7 @@
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="3"/>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
@@ -2659,7 +2706,7 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="3"/>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>11</v>
@@ -2670,7 +2717,9 @@
       <c r="E40" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G40" s="3" t="s">
         <v>30</v>
       </c>
@@ -2678,10 +2727,10 @@
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="3"/>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D41" s="3">
         <v>4</v>
@@ -2697,7 +2746,7 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="3"/>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>11</v>
@@ -2716,10 +2765,10 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="3"/>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D43" s="3">
         <v>4</v>
@@ -2735,13 +2784,13 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="3"/>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>30</v>
@@ -2754,13 +2803,13 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="3"/>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>30</v>
@@ -2773,18 +2822,20 @@
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="3"/>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D46" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>30</v>
       </c>
@@ -2792,13 +2843,13 @@
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="3"/>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>30</v>
@@ -2811,13 +2862,13 @@
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="3"/>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>30</v>
@@ -2830,13 +2881,13 @@
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="3"/>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>30</v>
@@ -2849,18 +2900,18 @@
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="3"/>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D50" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F50"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>30</v>
       </c>
@@ -2868,18 +2919,18 @@
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="3"/>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D51" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F51"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>30</v>
       </c>
@@ -2887,18 +2938,18 @@
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="3"/>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D52" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F52"/>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>30</v>
       </c>
@@ -2906,13 +2957,13 @@
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="3"/>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3.5</v>
+        <v>11</v>
+      </c>
+      <c r="D53" s="3">
+        <v>4</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>30</v>
@@ -2925,20 +2976,18 @@
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="3"/>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>30</v>
       </c>
@@ -2946,10 +2995,10 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="3"/>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D55" s="3">
         <v>3.5</v>
@@ -2965,10 +3014,10 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="3"/>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D56" s="3">
         <v>3.5</v>
@@ -2984,7 +3033,7 @@
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="3"/>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -3003,7 +3052,7 @@
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="3"/>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>11</v>
@@ -3022,10 +3071,10 @@
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="3"/>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D59" s="3">
         <v>3.5</v>
@@ -3033,7 +3082,7 @@
       <c r="E59" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59"/>
       <c r="G59" s="3" t="s">
         <v>30</v>
       </c>
@@ -3041,12 +3090,12 @@
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="3"/>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="3">
+        <v>15</v>
+      </c>
+      <c r="D60" s="6">
         <v>3.5</v>
       </c>
       <c r="E60" s="3" t="s">
@@ -3060,18 +3109,20 @@
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="3"/>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="3">
         <v>3.5</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G61" s="3" t="s">
         <v>30</v>
       </c>
@@ -3079,7 +3130,7 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="3"/>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>11</v>
@@ -3097,8 +3148,8 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="3"/>
-      <c r="B63" s="18" t="s">
-        <v>75</v>
+      <c r="B63" t="s">
+        <v>69</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
@@ -3117,7 +3168,7 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="3"/>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>11</v>
@@ -3136,10 +3187,10 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="3"/>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D65" s="3">
         <v>3.5</v>
@@ -3155,20 +3206,18 @@
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="3"/>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="6">
         <v>3.5</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>30</v>
       </c>
@@ -3176,7 +3225,7 @@
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" s="3"/>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>11</v>
@@ -3194,8 +3243,8 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" s="3"/>
-      <c r="B68" t="s">
-        <v>80</v>
+      <c r="B68" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
@@ -3214,7 +3263,7 @@
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="3"/>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>11</v>
@@ -3233,10 +3282,10 @@
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" s="3"/>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D70" s="3">
         <v>3.5</v>
@@ -3252,10 +3301,10 @@
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="3"/>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D71" s="3">
         <v>3.5</v>
@@ -3263,7 +3312,9 @@
       <c r="E71" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G71" s="3" t="s">
         <v>30</v>
       </c>
@@ -3271,10 +3322,10 @@
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="3"/>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D72" s="3">
         <v>3.5</v>
@@ -3290,10 +3341,10 @@
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="3"/>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D73" s="3">
         <v>3.5</v>
@@ -3309,10 +3360,10 @@
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="3"/>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D74" s="3">
         <v>3.5</v>
@@ -3328,10 +3379,10 @@
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="3"/>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D75" s="3">
         <v>3.5</v>
@@ -3347,7 +3398,7 @@
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="3"/>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
@@ -3366,7 +3417,7 @@
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="3"/>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>11</v>
@@ -3385,10 +3436,10 @@
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="3"/>
       <c r="B78" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D78" s="3">
         <v>3.5</v>
@@ -3404,7 +3455,7 @@
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="3"/>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -3423,7 +3474,7 @@
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" s="3"/>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
@@ -3442,7 +3493,7 @@
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="3"/>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>11</v>
@@ -3461,7 +3512,7 @@
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="3"/>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>11</v>
@@ -3480,10 +3531,10 @@
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="3"/>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D83" s="3">
         <v>3.5</v>
@@ -3499,7 +3550,7 @@
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="3"/>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>15</v>
@@ -3518,10 +3569,10 @@
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="3"/>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D85" s="3">
         <v>3.5</v>
@@ -3537,10 +3588,10 @@
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" s="3"/>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D86" s="3">
         <v>3.5</v>
@@ -3556,7 +3607,7 @@
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="3"/>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>11</v>
@@ -3575,7 +3626,7 @@
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" s="3"/>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -3594,7 +3645,7 @@
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="3"/>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -3613,7 +3664,7 @@
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="3"/>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
@@ -3632,10 +3683,10 @@
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="3"/>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D91" s="3">
         <v>3.5</v>
@@ -3651,10 +3702,10 @@
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="3"/>
       <c r="B92" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D92" s="3">
         <v>3.5</v>
@@ -3670,10 +3721,10 @@
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="3"/>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D93" s="3">
         <v>3.5</v>
@@ -3689,10 +3740,10 @@
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="3"/>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D94" s="3">
         <v>3.5</v>
@@ -3708,10 +3759,10 @@
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="3"/>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D95" s="3">
         <v>3.5</v>
@@ -3727,7 +3778,7 @@
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="3"/>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>11</v>
@@ -3746,7 +3797,7 @@
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="3"/>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>11</v>
@@ -3765,7 +3816,7 @@
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="3"/>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>11</v>
@@ -3784,7 +3835,7 @@
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="3"/>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>11</v>
@@ -3802,8 +3853,8 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="3"/>
-      <c r="B100" s="19" t="s">
-        <v>112</v>
+      <c r="B100" t="s">
+        <v>108</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>11</v>
@@ -3821,8 +3872,8 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="3"/>
-      <c r="B101" s="19" t="s">
-        <v>112</v>
+      <c r="B101" t="s">
+        <v>109</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>11</v>
@@ -3841,10 +3892,10 @@
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="3"/>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D102" s="3">
         <v>3.5</v>
@@ -3860,10 +3911,10 @@
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="3"/>
       <c r="B103" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D103" s="3">
         <v>3.5</v>
@@ -3878,14 +3929,14 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="3"/>
-      <c r="B104" t="s">
-        <v>114</v>
+      <c r="B104" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D104" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>30</v>
@@ -3897,14 +3948,14 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="3"/>
-      <c r="B105" t="s">
-        <v>115</v>
+      <c r="B105" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>30</v>
@@ -3916,14 +3967,14 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="3"/>
-      <c r="B106" s="19" t="s">
-        <v>116</v>
+      <c r="B106" t="s">
+        <v>113</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D106" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>30</v>
@@ -3936,13 +3987,13 @@
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="3"/>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D107" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>30</v>
@@ -3955,10 +4006,10 @@
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="3"/>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D108" s="3">
         <v>3</v>
@@ -3973,8 +4024,8 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="3"/>
-      <c r="B109" t="s">
-        <v>119</v>
+      <c r="B109" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>11</v>
@@ -3993,7 +4044,7 @@
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="3"/>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>11</v>
@@ -4012,10 +4063,10 @@
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="3"/>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D111" s="3">
         <v>3</v>
@@ -4031,7 +4082,7 @@
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="3"/>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>11</v>
@@ -4050,7 +4101,7 @@
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="3"/>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>11</v>
@@ -4069,7 +4120,7 @@
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="3"/>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>11</v>
@@ -4087,11 +4138,11 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="3"/>
-      <c r="B115" s="18" t="s">
-        <v>124</v>
+      <c r="B115" t="s">
+        <v>67</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D115" s="3">
         <v>3</v>
@@ -4107,7 +4158,7 @@
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="3"/>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>11</v>
@@ -4126,7 +4177,7 @@
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="3"/>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>11</v>
@@ -4144,11 +4195,11 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="3"/>
-      <c r="B118" t="s">
-        <v>127</v>
+      <c r="B118" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D118" s="3">
         <v>3</v>
@@ -4164,7 +4215,7 @@
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="3"/>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>11</v>
@@ -4183,7 +4234,7 @@
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="3"/>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>11</v>
@@ -4202,10 +4253,10 @@
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="3"/>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D121" s="3">
         <v>3</v>
@@ -4221,10 +4272,10 @@
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="3"/>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D122" s="3">
         <v>3</v>
@@ -4240,7 +4291,7 @@
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="3"/>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>15</v>
@@ -4259,7 +4310,7 @@
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="3"/>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>15</v>
@@ -4278,10 +4329,10 @@
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="3"/>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D125" s="3">
         <v>3</v>
@@ -4297,10 +4348,10 @@
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="3"/>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D126" s="3">
         <v>3</v>
@@ -4316,7 +4367,7 @@
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="3"/>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>11</v>
@@ -4335,7 +4386,7 @@
     <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" s="3"/>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>11</v>
@@ -4354,7 +4405,7 @@
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="3"/>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>11</v>
@@ -4373,10 +4424,10 @@
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="3"/>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D130" s="3">
         <v>3</v>
@@ -4392,10 +4443,10 @@
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="3"/>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D131" s="3">
         <v>3</v>
@@ -4411,7 +4462,7 @@
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="3"/>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>15</v>
@@ -4430,7 +4481,7 @@
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="3"/>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>15</v>
@@ -4449,7 +4500,7 @@
     <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="3"/>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>15</v>
@@ -4468,10 +4519,10 @@
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="3"/>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D135" s="3">
         <v>3</v>
@@ -4487,7 +4538,7 @@
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="3"/>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>15</v>
@@ -4506,10 +4557,10 @@
     <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="3"/>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D137" s="3">
         <v>3</v>
@@ -4525,7 +4576,7 @@
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="3"/>
       <c r="B138" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>15</v>
@@ -4544,13 +4595,13 @@
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="3"/>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D139" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>30</v>
@@ -4563,13 +4614,13 @@
     <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="3"/>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D140" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>30</v>
@@ -4582,10 +4633,10 @@
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="3"/>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D141" s="3">
         <v>2.5</v>
@@ -4601,10 +4652,10 @@
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="3"/>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D142" s="3">
         <v>2.5</v>
@@ -4620,7 +4671,7 @@
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="3"/>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>11</v>
@@ -4639,7 +4690,7 @@
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="3"/>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>11</v>
@@ -4658,18 +4709,18 @@
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" s="3"/>
       <c r="B145" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D145" s="6">
-        <v>1.5</v>
+        <v>11</v>
+      </c>
+      <c r="D145" s="3">
+        <v>2.5</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F145"/>
+      <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
         <v>30</v>
       </c>
@@ -4677,18 +4728,18 @@
     <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" s="3"/>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D146" s="6">
-        <v>1.5</v>
+        <v>11</v>
+      </c>
+      <c r="D146" s="3">
+        <v>2.5</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F146"/>
+      <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
         <v>30</v>
       </c>
@@ -4696,7 +4747,7 @@
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="3"/>
       <c r="B147" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>15</v>
@@ -4712,9 +4763,47 @@
         <v>30</v>
       </c>
     </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148" s="3"/>
+      <c r="B148" t="s">
+        <v>146</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F148"/>
+      <c r="G148" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A149" s="3"/>
+      <c r="B149" t="s">
+        <v>133</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F149"/>
+      <c r="G149" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G119" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G147">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G149">
       <sortCondition ref="A1:A119"/>
     </sortState>
   </autoFilter>
@@ -4841,117 +4930,117 @@
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="22" t="s">
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="22" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="22" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="22" t="s">
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="22"/>
       <c r="AA1" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="22" t="s">
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="21"/>
+      <c r="AH1" s="21"/>
+      <c r="AI1" s="21"/>
+      <c r="AJ1" s="21"/>
+      <c r="AK1" s="22"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" s="13"/>
       <c r="B2" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22">
-        <v>1</v>
-      </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="22">
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="20">
+        <v>1</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="20">
         <v>0</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="22">
-        <v>1</v>
-      </c>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="22">
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="20">
+        <v>1</v>
+      </c>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="20">
         <v>0</v>
       </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="22">
-        <v>1</v>
-      </c>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="20">
+        <v>1</v>
+      </c>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="22"/>
       <c r="AA2" s="24">
         <v>4</v>
       </c>
-      <c r="AB2" s="21"/>
+      <c r="AB2" s="22"/>
       <c r="AC2" s="24">
         <v>4</v>
       </c>
-      <c r="AD2" s="21"/>
+      <c r="AD2" s="22"/>
       <c r="AE2" s="24">
         <v>8</v>
       </c>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="22">
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="20">
         <v>0</v>
       </c>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="22"/>
       <c r="AK2" s="14">
         <v>1</v>
       </c>
@@ -5114,16 +5203,16 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB4" s="21"/>
+      <c r="AA4" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4" s="22"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="15"/>
-      <c r="AE4" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF4" s="21"/>
+      <c r="AE4" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF4" s="22"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
@@ -5175,16 +5264,16 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB5" s="21"/>
+      <c r="AA5" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB5" s="22"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="15"/>
-      <c r="AE5" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF5" s="21"/>
+      <c r="AE5" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF5" s="22"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -5236,16 +5325,16 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB6" s="21"/>
+      <c r="AA6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB6" s="22"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="15"/>
-      <c r="AE6" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF6" s="21"/>
+      <c r="AE6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF6" s="22"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -5305,18 +5394,18 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF7" s="21"/>
+      <c r="AA7" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF7" s="22"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -5378,18 +5467,18 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD8" s="21"/>
-      <c r="AE8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF8" s="21"/>
+      <c r="AA8" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF8" s="22"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -5453,18 +5542,18 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD9" s="21"/>
-      <c r="AE9" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF9" s="21"/>
+      <c r="AA9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF9" s="22"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -5526,18 +5615,18 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB10" s="21"/>
-      <c r="AC10" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD10" s="21"/>
-      <c r="AE10" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF10" s="21"/>
+      <c r="AA10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF10" s="22"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
@@ -5599,18 +5688,18 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF11" s="21"/>
+      <c r="AA11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF11" s="22"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -5670,18 +5759,18 @@
         <v>30</v>
       </c>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF12" s="21"/>
+      <c r="AA12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF12" s="22"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
@@ -5739,18 +5828,18 @@
         <v>30</v>
       </c>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF13" s="21"/>
+      <c r="AA13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF13" s="22"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -5810,18 +5899,18 @@
         <v>30</v>
       </c>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF14" s="21"/>
+      <c r="AA14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF14" s="22"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
@@ -5879,18 +5968,18 @@
         <v>30</v>
       </c>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF15" s="21"/>
+      <c r="AA15" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF15" s="22"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
@@ -5948,18 +6037,18 @@
         <v>30</v>
       </c>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF16" s="21"/>
+      <c r="AA16" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF16" s="22"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
@@ -6003,18 +6092,18 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH17" s="21"/>
+      <c r="AC17" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF17" s="22"/>
+      <c r="AG17" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH17" s="22"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="11" t="s">
@@ -6058,18 +6147,18 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH18" s="21"/>
+      <c r="AC18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF18" s="22"/>
+      <c r="AG18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH18" s="22"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="11" t="s">
@@ -6115,18 +6204,18 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH19" s="21"/>
+      <c r="AC19" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH19" s="22"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="11" t="s">
@@ -6138,11 +6227,48 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AD15"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="AC8:AD8"/>
+    <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="AE10:AF10"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AE11:AF11"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC17:AD17"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AE17:AF17"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="AE13:AF13"/>
@@ -6159,48 +6285,11 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="AE10:AF10"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AE18:AF18"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AD15"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="AC8:AD8"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="W2:Z2"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AE8:AF8"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AC17:AD17"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AC19:AD19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -78,6 +78,19 @@
     <font>
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="3"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
@@ -196,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -253,16 +266,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -857,7 +873,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>🔴吉永</t>
+          <t>🔴ともだ</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -866,7 +882,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
@@ -895,7 +911,7 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>🔵前田</t>
+          <t>🔵こばたく</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -910,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1</v>
@@ -933,7 +949,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>🔴もーちゃん</t>
+          <t>🔴たぬき</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -942,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -971,12 +987,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>🔴美玖</t>
+          <t>🔵安田たかひろ</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1009,12 +1025,12 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>🔴あすか</t>
+          <t>🔵Sa Fu</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1024,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
@@ -1047,12 +1063,12 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>🔴えりな</t>
+          <t>🔵三田</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1085,7 +1101,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>🔴未来</t>
+          <t>🔴のどか</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -1123,12 +1139,12 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆい</t>
+          <t>🔵とみー</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1161,16 +1177,16 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆきえ</t>
+          <t>🔵しゅうた</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1</v>
@@ -1199,7 +1215,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>🔴まいぴ</t>
+          <t>🔴ぱるる</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -1208,7 +1224,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
@@ -1237,16 +1253,16 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>🔴ともみ</t>
+          <t>🔵前田</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1</v>
@@ -1275,7 +1291,7 @@
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆうか</t>
+          <t>🔴えりな</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1308,80 +1324,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>🔵shunpon</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>待機</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="0" t="n"/>
+      <c r="C18" s="0" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="0" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>🔵加地</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>待機</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="0" t="n"/>
+      <c r="C19" s="0" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1551,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="13.59765625" customWidth="1" style="6" min="1" max="1"/>
@@ -1681,13 +1645,21 @@
       <c r="D4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1728,7 +1700,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>🔴吉永</t>
+          <t>🔴ともだ</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1737,7 +1709,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -1759,7 +1731,7 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>🔵前田</t>
+          <t>🔵こばたく</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1775,7 +1747,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1790,7 +1766,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>🔴もーちゃん</t>
+          <t>🔴たぬき</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1799,7 +1775,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -1821,12 +1797,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>🔴美玖</t>
+          <t>🔵安田たかひろ</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1837,7 +1813,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1845,19 +1821,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>🔴あすか</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>🔵Sa Fu</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1868,7 +1844,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1883,15 +1863,15 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>🔴えりな</t>
+          <t>🔵三田</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1899,7 +1879,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1914,7 +1894,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>🔴未来</t>
+          <t>🔴のどか</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1922,7 +1902,7 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1930,7 +1910,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1945,15 +1925,15 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆい</t>
+          <t>🔵とみー</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1961,7 +1941,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -1976,23 +1956,23 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆきえ</t>
+          <t>🔵しゅうた</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>3.5</v>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2000,14 +1980,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>🔴まいぴ</t>
+          <t>🔴ぱるる</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2016,14 +1996,14 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2038,16 +2018,16 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>🔴ともみ</t>
+          <t>🔵前田</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2062,14 +2042,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆうか</t>
+          <t>🔴えりな</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2077,7 +2057,7 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2085,7 +2065,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2093,23 +2073,19 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>🔵shunpon</t>
+          <t>🔴吉永</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>3</v>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3.5</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -2124,23 +2100,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="inlineStr"/>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>🔵加地</t>
+          <t>🔴もーちゃん</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -2158,7 +2130,7 @@
       <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>🔴ひろみ</t>
+          <t>🔴美玖</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2167,14 +2139,14 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2185,7 +2157,7 @@
       <c r="A21" s="3" t="inlineStr"/>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>🔴ともだ</t>
+          <t>🔴あすか</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2193,15 +2165,15 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
-        <v>4</v>
+      <c r="D21" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2212,39 +2184,43 @@
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>🔵てぃの</t>
+          <t>🔴未来</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>🔵きなり</t>
+          <t>🔴ゆい</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -2262,27 +2238,23 @@
       <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>🔵今枝</t>
+          <t>🔴ゆきえ</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2290,10 +2262,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>🔴森</t>
+          <t>🔴まいぴ</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2301,19 +2273,15 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>4</v>
+      <c r="D25" s="6" t="n">
+        <v>3.5</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F25" s="0" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2324,27 +2292,23 @@
       <c r="A26" s="3" t="inlineStr"/>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>🔵高木</t>
+          <t>🔴ともみ</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>4</v>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2352,30 +2316,26 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>🔵たっちゃん</t>
+          <t>🔴ゆうか</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F27" s="0" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2386,7 +2346,7 @@
       <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>🔵たかはしかい</t>
+          <t>🔵shunpon</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2394,19 +2354,15 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>4</v>
+      <c r="D28" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2417,7 +2373,7 @@
       <c r="A29" s="3" t="inlineStr"/>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>🔵ふるさわ</t>
+          <t>🔵加地</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2425,19 +2381,15 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
-        <v>4</v>
+      <c r="D29" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2448,15 +2400,15 @@
       <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>🔵納富</t>
+          <t>🔴ひろみ</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n">
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2464,7 +2416,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F30" s="0" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2475,7 +2427,7 @@
       <c r="A31" s="3" t="inlineStr"/>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>🔵むね</t>
+          <t>🔵てぃの</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2486,27 +2438,19 @@
       <c r="D31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>🔵すぐる</t>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>🔵きなり</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2533,12 +2477,12 @@
       <c r="A33" s="3" t="inlineStr"/>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>🔴ななこ</t>
+          <t>🔵今枝</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2549,7 +2493,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2560,7 +2508,7 @@
       <c r="A34" s="3" t="inlineStr"/>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>🔴まや</t>
+          <t>🔴森</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2576,7 +2524,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2587,7 +2539,7 @@
       <c r="A35" s="3" t="inlineStr"/>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>🔵かいと</t>
+          <t>🔵高木</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2595,7 +2547,7 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2603,7 +2555,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2614,7 +2570,7 @@
       <c r="A36" s="3" t="inlineStr"/>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>🔵松平</t>
+          <t>🔵たっちゃん</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2630,7 +2586,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2641,7 +2601,7 @@
       <c r="A37" s="3" t="inlineStr"/>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>🔵なんば</t>
+          <t>🔵たかはしかい</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2657,7 +2617,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2668,7 +2632,7 @@
       <c r="A38" s="3" t="inlineStr"/>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>🔵落合</t>
+          <t>🔵ふるさわ</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2676,7 +2640,7 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2684,7 +2648,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2695,7 +2663,7 @@
       <c r="A39" s="3" t="inlineStr"/>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>🔵望月</t>
+          <t>🔵納富</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2703,7 +2671,7 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2711,7 +2679,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
+      <c r="F39" s="0" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2722,7 +2690,7 @@
       <c r="A40" s="3" t="inlineStr"/>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>🔵ゆうた</t>
+          <t>🔵むね</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2751,9 +2719,9 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr"/>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>🔵しんげん</t>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>🔵すぐる</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2780,12 +2748,12 @@
       <c r="A42" s="3" t="inlineStr"/>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>🔵渡邊</t>
+          <t>🔴ななこ</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -2807,7 +2775,7 @@
       <c r="A43" s="3" t="inlineStr"/>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>🔴よこゆか</t>
+          <t>🔴まや</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2834,7 +2802,7 @@
       <c r="A44" s="3" t="inlineStr"/>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>🔵三田</t>
+          <t>🔵かいと</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2861,15 +2829,15 @@
       <c r="A45" s="3" t="inlineStr"/>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>🔴まひろ</t>
+          <t>🔵松平</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2877,7 +2845,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
+      <c r="F45" s="0" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2888,7 +2856,7 @@
       <c r="A46" s="3" t="inlineStr"/>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>🔵こばやし</t>
+          <t>🔵なんば</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2896,7 +2864,7 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2904,11 +2872,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -2919,12 +2883,12 @@
       <c r="A47" s="3" t="inlineStr"/>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>🔴小熊</t>
+          <t>🔵落合</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -2946,7 +2910,7 @@
       <c r="A48" s="3" t="inlineStr"/>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>🔵秋山</t>
+          <t>🔵望月</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2973,12 +2937,12 @@
       <c r="A49" s="3" t="inlineStr"/>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>🔴石川</t>
+          <t>🔵ゆうた</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -2989,7 +2953,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3000,7 +2968,7 @@
       <c r="A50" s="3" t="inlineStr"/>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>🔵野澤</t>
+          <t>🔵しんげん</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3027,7 +2995,7 @@
       <c r="A51" s="3" t="inlineStr"/>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>🔵根津</t>
+          <t>🔵渡邊</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3054,7 +3022,7 @@
       <c r="A52" s="3" t="inlineStr"/>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>🔴すわめん</t>
+          <t>🔴よこゆか</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3081,7 +3049,7 @@
       <c r="A53" s="3" t="inlineStr"/>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>🔵山口</t>
+          <t>🔵三田</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3108,12 +3076,12 @@
       <c r="A54" s="3" t="inlineStr"/>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>🔵天野</t>
+          <t>🔴まひろ</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -3135,7 +3103,7 @@
       <c r="A55" s="3" t="inlineStr"/>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>🔴たぬき</t>
+          <t>🔴小熊</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3144,7 +3112,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3162,7 +3130,7 @@
       <c r="A56" s="3" t="inlineStr"/>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>🔵またがわ</t>
+          <t>🔵秋山</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3171,7 +3139,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3189,7 +3157,7 @@
       <c r="A57" s="3" t="inlineStr"/>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>🔴なるみ</t>
+          <t>🔴石川</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3198,7 +3166,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -3216,7 +3184,7 @@
       <c r="A58" s="3" t="inlineStr"/>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>🔵西郷</t>
+          <t>🔵野澤</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3225,7 +3193,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3211,7 @@
       <c r="A59" s="3" t="inlineStr"/>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>🔵津島</t>
+          <t>🔵根津</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3252,14 +3220,14 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F59" s="0" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3270,7 +3238,7 @@
       <c r="A60" s="3" t="inlineStr"/>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>🔴せぶん</t>
+          <t>🔴すわめん</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3278,8 +3246,8 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>3.5</v>
+      <c r="D60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -3297,7 +3265,7 @@
       <c r="A61" s="3" t="inlineStr"/>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>🔵古澤哲</t>
+          <t>🔵山口</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3306,18 +3274,14 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3328,7 +3292,7 @@
       <c r="A62" s="3" t="inlineStr"/>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>🔵林</t>
+          <t>🔵天野</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3337,7 +3301,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -3355,12 +3319,12 @@
       <c r="A63" s="3" t="inlineStr"/>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>🔴いっちゃん</t>
+          <t>🔵またがわ</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -3382,12 +3346,12 @@
       <c r="A64" s="3" t="inlineStr"/>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>🔵うっしー</t>
+          <t>🔴なるみ</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -3409,7 +3373,7 @@
       <c r="A65" s="3" t="inlineStr"/>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>🔵キタ</t>
+          <t>🔵西郷</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3436,7 +3400,7 @@
       <c r="A66" s="3" t="inlineStr"/>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>🔵よっしー</t>
+          <t>🔵津島</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3444,7 +3408,7 @@
           <t>男</t>
         </is>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3452,7 +3416,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
+      <c r="F66" s="0" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3463,15 +3427,15 @@
       <c r="A67" s="3" t="inlineStr"/>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>🔵ならい</t>
+          <t>🔴せぶん</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -3488,14 +3452,14 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr"/>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>🔴しゅり</t>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>🔵古澤哲</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -3506,7 +3470,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3517,7 +3485,7 @@
       <c r="A69" s="3" t="inlineStr"/>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>🔵安田たかひろ</t>
+          <t>🔵林</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3544,7 +3512,7 @@
       <c r="A70" s="3" t="inlineStr"/>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>🔴ともね</t>
+          <t>🔴いっちゃん</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3571,7 +3539,7 @@
       <c r="A71" s="3" t="inlineStr"/>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>🔵小出直人</t>
+          <t>🔵うっしー</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3587,11 +3555,7 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3602,7 +3566,7 @@
       <c r="A72" s="3" t="inlineStr"/>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>🔵ゆうや</t>
+          <t>🔵キタ</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3629,15 +3593,15 @@
       <c r="A73" s="3" t="inlineStr"/>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>🔴はるか</t>
+          <t>🔵よっしー</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -3656,7 +3620,7 @@
       <c r="A74" s="3" t="inlineStr"/>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>🔵ぐっぴー</t>
+          <t>🔵ならい</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3681,14 +3645,14 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr"/>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>🔵なお</t>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>🔴しゅり</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
@@ -3710,7 +3674,7 @@
       <c r="A76" s="3" t="inlineStr"/>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>🔴れいか</t>
+          <t>🔴ともね</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3737,7 +3701,7 @@
       <c r="A77" s="3" t="inlineStr"/>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>🔵石上</t>
+          <t>🔵小出直人</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -3753,7 +3717,11 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -3764,12 +3732,12 @@
       <c r="A78" s="3" t="inlineStr"/>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>🔴西尾</t>
+          <t>🔵ゆうや</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -3791,7 +3759,7 @@
       <c r="A79" s="3" t="inlineStr"/>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>🔴中瀬</t>
+          <t>🔴はるか</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3818,12 +3786,12 @@
       <c r="A80" s="3" t="inlineStr"/>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>🔴ののの_</t>
+          <t>🔵ぐっぴー</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
@@ -3845,7 +3813,7 @@
       <c r="A81" s="3" t="inlineStr"/>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>🔵ぴー</t>
+          <t>🔵なお</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3872,12 +3840,12 @@
       <c r="A82" s="3" t="inlineStr"/>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>🔵かずま</t>
+          <t>🔴れいか</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -3899,12 +3867,12 @@
       <c r="A83" s="3" t="inlineStr"/>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>🔴かつまた</t>
+          <t>🔵石上</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -3926,7 +3894,7 @@
       <c r="A84" s="3" t="inlineStr"/>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>🔴なお</t>
+          <t>🔴西尾</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3953,12 +3921,12 @@
       <c r="A85" s="3" t="inlineStr"/>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>🔵そーま</t>
+          <t>🔴中瀬</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
@@ -3980,12 +3948,12 @@
       <c r="A86" s="3" t="inlineStr"/>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>🔵こしいし</t>
+          <t>🔴ののの_</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -4007,7 +3975,7 @@
       <c r="A87" s="3" t="inlineStr"/>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>🔵格之進</t>
+          <t>🔵ぴー</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4034,12 +4002,12 @@
       <c r="A88" s="3" t="inlineStr"/>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>🔴友田</t>
+          <t>🔵かずま</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -4061,7 +4029,7 @@
       <c r="A89" s="3" t="inlineStr"/>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>🔴よう</t>
+          <t>🔴かつまた</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4088,7 +4056,7 @@
       <c r="A90" s="3" t="inlineStr"/>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>🔴小林友人</t>
+          <t>🔴なお</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4115,7 +4083,7 @@
       <c r="A91" s="3" t="inlineStr"/>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>🔵平山</t>
+          <t>🔵そーま</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -4142,12 +4110,12 @@
       <c r="A92" s="3" t="inlineStr"/>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>🔴そが</t>
+          <t>🔵こしいし</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -4169,12 +4137,12 @@
       <c r="A93" s="3" t="inlineStr"/>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>🔴柴田</t>
+          <t>🔵格之進</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
@@ -4196,7 +4164,7 @@
       <c r="A94" s="3" t="inlineStr"/>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>🔴chie</t>
+          <t>🔴友田</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -4223,7 +4191,7 @@
       <c r="A95" s="3" t="inlineStr"/>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>🔴せーな</t>
+          <t>🔴よう</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -4250,12 +4218,12 @@
       <c r="A96" s="3" t="inlineStr"/>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>🔵桐下</t>
+          <t>🔴小林友人</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -4277,7 +4245,7 @@
       <c r="A97" s="3" t="inlineStr"/>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>🔵さいとう</t>
+          <t>🔵平山</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4304,12 +4272,12 @@
       <c r="A98" s="3" t="inlineStr"/>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>🔵サトシ</t>
+          <t>🔴そが</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -4331,12 +4299,12 @@
       <c r="A99" s="3" t="inlineStr"/>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>🔵谷村</t>
+          <t>🔴柴田</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
@@ -4358,12 +4326,12 @@
       <c r="A100" s="3" t="inlineStr"/>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>🔵にっしー</t>
+          <t>🔴chie</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -4385,12 +4353,12 @@
       <c r="A101" s="3" t="inlineStr"/>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>🔵はしもと</t>
+          <t>🔴せーな</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
@@ -4412,7 +4380,7 @@
       <c r="A102" s="3" t="inlineStr"/>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>🔵ひろき</t>
+          <t>🔵桐下</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4439,7 +4407,7 @@
       <c r="A103" s="3" t="inlineStr"/>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>🔵ゆう</t>
+          <t>🔵さいとう</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4464,9 +4432,9 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr"/>
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>🔵[FREE_中]</t>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>🔵サトシ</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4491,9 +4459,9 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr"/>
-      <c r="B105" s="19" t="inlineStr">
-        <is>
-          <t>🔵[FREE_中]</t>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>🔵谷村</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4520,12 +4488,12 @@
       <c r="A106" s="3" t="inlineStr"/>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>🔴[FREE_中]</t>
+          <t>🔵にっしー</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -4547,12 +4515,12 @@
       <c r="A107" s="3" t="inlineStr"/>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>🔴[FREE_中]</t>
+          <t>🔵はしもと</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
@@ -4574,7 +4542,7 @@
       <c r="A108" s="3" t="inlineStr"/>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>🔵吉野</t>
+          <t>🔵ひろき</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4583,7 +4551,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -4599,9 +4567,9 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr"/>
-      <c r="B109" s="19" t="inlineStr">
-        <is>
-          <t>🔵ゆーみ</t>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>🔵ゆう</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4610,7 +4578,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -4626,9 +4594,9 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr"/>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>🔵リョウ</t>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>🔵[FREE_中]</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4637,7 +4605,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -4653,18 +4621,18 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr"/>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t>🔴hama</t>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>🔵[FREE_中]</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -4682,16 +4650,16 @@
       <c r="A112" s="3" t="inlineStr"/>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>🔵たつや</t>
+          <t>🔴[FREE_中]</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -4709,16 +4677,16 @@
       <c r="A113" s="3" t="inlineStr"/>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>🔵Gen</t>
+          <t>🔴[FREE_中]</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4736,7 +4704,7 @@
       <c r="A114" s="3" t="inlineStr"/>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>🔵金カツ</t>
+          <t>🔵吉野</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4761,9 +4729,9 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr"/>
-      <c r="B115" s="0" t="inlineStr">
-        <is>
-          <t>🔵林</t>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>🔵ゆーみ</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4790,7 +4758,7 @@
       <c r="A116" s="3" t="inlineStr"/>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>🔵にわ</t>
+          <t>🔵リョウ</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4817,12 +4785,12 @@
       <c r="A117" s="3" t="inlineStr"/>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>🔵のっぽ</t>
+          <t>🔴hama</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
@@ -4842,14 +4810,14 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr"/>
-      <c r="B118" s="18" t="inlineStr">
-        <is>
-          <t>🔴えりんご</t>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>🔵たつや</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -4871,7 +4839,7 @@
       <c r="A119" s="3" t="inlineStr"/>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>🔵そう</t>
+          <t>🔵Gen</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4898,7 +4866,7 @@
       <c r="A120" s="3" t="inlineStr"/>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>🔵かつき</t>
+          <t>🔵金カツ</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4925,7 +4893,7 @@
       <c r="A121" s="3" t="inlineStr"/>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>🔵臼井</t>
+          <t>🔵林</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4952,7 +4920,7 @@
       <c r="A122" s="3" t="inlineStr"/>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>🔵柴田_</t>
+          <t>🔵にわ</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4979,12 +4947,12 @@
       <c r="A123" s="3" t="inlineStr"/>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>🔴綾香</t>
+          <t>🔵のっぽ</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
@@ -5004,9 +4972,9 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr"/>
-      <c r="B124" s="0" t="inlineStr">
-        <is>
-          <t>🔴さとみ</t>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>🔴えりんご</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -5033,12 +5001,12 @@
       <c r="A125" s="3" t="inlineStr"/>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>🔴朋子</t>
+          <t>🔵そう</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
@@ -5060,12 +5028,12 @@
       <c r="A126" s="3" t="inlineStr"/>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>🔴ゆき</t>
+          <t>🔵かつき</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -5087,7 +5055,7 @@
       <c r="A127" s="3" t="inlineStr"/>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>🔵金子</t>
+          <t>🔵臼井</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -5114,7 +5082,7 @@
       <c r="A128" s="3" t="inlineStr"/>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>🔵しばた</t>
+          <t>🔵柴田_</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -5141,12 +5109,12 @@
       <c r="A129" s="3" t="inlineStr"/>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>🔵下田</t>
+          <t>🔴綾香</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -5168,12 +5136,12 @@
       <c r="A130" s="3" t="inlineStr"/>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>🔵山田</t>
+          <t>🔴さとみ</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -5195,12 +5163,12 @@
       <c r="A131" s="3" t="inlineStr"/>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>🔵りょうすけ</t>
+          <t>🔴朋子</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -5222,7 +5190,7 @@
       <c r="A132" s="3" t="inlineStr"/>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>🔴あすみ</t>
+          <t>🔴ゆき</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -5249,12 +5217,12 @@
       <c r="A133" s="3" t="inlineStr"/>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>🔴ななみ</t>
+          <t>🔵金子</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -5276,12 +5244,12 @@
       <c r="A134" s="3" t="inlineStr"/>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>🔴はまぐち_</t>
+          <t>🔵しばた</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -5303,12 +5271,12 @@
       <c r="A135" s="3" t="inlineStr"/>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>🔴chika</t>
+          <t>🔵下田</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -5330,12 +5298,12 @@
       <c r="A136" s="3" t="inlineStr"/>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>🔴ななみ</t>
+          <t>🔵山田</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -5357,7 +5325,7 @@
       <c r="A137" s="3" t="inlineStr"/>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>🔵チンシケツ</t>
+          <t>🔵りょうすけ</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -5384,7 +5352,7 @@
       <c r="A138" s="3" t="inlineStr"/>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>🔴まき</t>
+          <t>🔴あすみ</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -5411,7 +5379,7 @@
       <c r="A139" s="3" t="inlineStr"/>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>🔴わかな</t>
+          <t>🔴ななみ</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -5438,7 +5406,7 @@
       <c r="A140" s="3" t="inlineStr"/>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>🔴かつまた</t>
+          <t>🔴はまぐち_</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -5465,7 +5433,7 @@
       <c r="A141" s="3" t="inlineStr"/>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>🔴さき</t>
+          <t>🔴chika</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -5474,7 +5442,7 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -5492,7 +5460,7 @@
       <c r="A142" s="3" t="inlineStr"/>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>🔴シャンシャン</t>
+          <t>🔴ななみ</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -5501,7 +5469,7 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -5519,7 +5487,7 @@
       <c r="A143" s="3" t="inlineStr"/>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>🔵スシャント</t>
+          <t>🔵チンシケツ</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -5528,7 +5496,7 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -5546,16 +5514,16 @@
       <c r="A144" s="3" t="inlineStr"/>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>🔵ICHIJIKU</t>
+          <t>🔴まき</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -5573,16 +5541,16 @@
       <c r="A145" s="3" t="inlineStr"/>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>🔵はしば</t>
+          <t>🔴わかな</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5600,16 +5568,16 @@
       <c r="A146" s="3" t="inlineStr"/>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>🔵せいたろう</t>
+          <t>🔴かつまた</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5627,7 +5595,7 @@
       <c r="A147" s="3" t="inlineStr"/>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>🔴しゅり</t>
+          <t>🔴さき</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -5635,15 +5603,15 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D147" s="6" t="n">
-        <v>1.5</v>
+      <c r="D147" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F147" s="0" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -5654,7 +5622,7 @@
       <c r="A148" s="3" t="inlineStr"/>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>🔴さき</t>
+          <t>🔴シャンシャン</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -5662,15 +5630,15 @@
           <t>女</t>
         </is>
       </c>
-      <c r="D148" s="6" t="n">
-        <v>1.5</v>
+      <c r="D148" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F148" s="0" t="inlineStr"/>
+      <c r="F148" s="3" t="inlineStr"/>
       <c r="G148" s="3" t="inlineStr">
         <is>
           <t>〇</t>
@@ -5681,33 +5649,195 @@
       <c r="A149" s="3" t="inlineStr"/>
       <c r="B149" s="0" t="inlineStr">
         <is>
+          <t>🔵スシャント</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr"/>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>🔵ICHIJIKU</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr"/>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr"/>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>🔵はしば</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr"/>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr"/>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t>🔵せいたろう</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr"/>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>🔴しゅり</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F153" s="0" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr"/>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>🔴さき</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F154" s="0" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr"/>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
           <t>🔴ゆき</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="n">
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F149" s="0" t="inlineStr"/>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-    </row>
-    <row r="150"/>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F155" s="0" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+    </row>
+    <row r="156"/>
   </sheetData>
   <autoFilter ref="A1:G119">
-    <sortState ref="A2:G149">
+    <sortState ref="A2:G155">
       <sortCondition ref="A1:A119"/>
     </sortState>
   </autoFilter>
@@ -5865,73 +5995,73 @@
     <row r="1">
       <c r="A1" s="13" t="n"/>
       <c r="B1" s="13" t="n"/>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>上級</t>
         </is>
       </c>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="22" t="n"/>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="D1" s="23" t="n"/>
+      <c r="E1" s="23" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>中/上級</t>
         </is>
       </c>
-      <c r="H1" s="21" t="n"/>
-      <c r="I1" s="21" t="n"/>
-      <c r="J1" s="22" t="n"/>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="H1" s="23" t="n"/>
+      <c r="I1" s="23" t="n"/>
+      <c r="J1" s="21" t="n"/>
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>中級</t>
         </is>
       </c>
-      <c r="L1" s="21" t="n"/>
-      <c r="M1" s="21" t="n"/>
-      <c r="N1" s="22" t="n"/>
-      <c r="O1" s="20" t="inlineStr">
+      <c r="L1" s="23" t="n"/>
+      <c r="M1" s="23" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="22" t="inlineStr">
         <is>
           <t>初/中級</t>
         </is>
       </c>
-      <c r="P1" s="21" t="n"/>
-      <c r="Q1" s="21" t="n"/>
-      <c r="R1" s="22" t="n"/>
-      <c r="S1" s="20" t="inlineStr">
+      <c r="P1" s="23" t="n"/>
+      <c r="Q1" s="23" t="n"/>
+      <c r="R1" s="21" t="n"/>
+      <c r="S1" s="22" t="inlineStr">
         <is>
           <t>初級</t>
         </is>
       </c>
-      <c r="T1" s="21" t="n"/>
-      <c r="U1" s="21" t="n"/>
-      <c r="V1" s="22" t="n"/>
-      <c r="W1" s="20" t="inlineStr">
+      <c r="T1" s="23" t="n"/>
+      <c r="U1" s="23" t="n"/>
+      <c r="V1" s="21" t="n"/>
+      <c r="W1" s="22" t="inlineStr">
         <is>
           <t>初/初級者</t>
         </is>
       </c>
-      <c r="X1" s="21" t="n"/>
-      <c r="Y1" s="21" t="n"/>
-      <c r="Z1" s="22" t="n"/>
+      <c r="X1" s="23" t="n"/>
+      <c r="Y1" s="23" t="n"/>
+      <c r="Z1" s="21" t="n"/>
       <c r="AA1" s="24" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
-      <c r="AB1" s="21" t="n"/>
-      <c r="AC1" s="21" t="n"/>
-      <c r="AD1" s="21" t="n"/>
-      <c r="AE1" s="21" t="n"/>
-      <c r="AF1" s="22" t="n"/>
-      <c r="AG1" s="20" t="inlineStr">
+      <c r="AB1" s="23" t="n"/>
+      <c r="AC1" s="23" t="n"/>
+      <c r="AD1" s="23" t="n"/>
+      <c r="AE1" s="23" t="n"/>
+      <c r="AF1" s="21" t="n"/>
+      <c r="AG1" s="22" t="inlineStr">
         <is>
           <t>初心者</t>
         </is>
       </c>
-      <c r="AH1" s="21" t="n"/>
-      <c r="AI1" s="21" t="n"/>
-      <c r="AJ1" s="21" t="n"/>
-      <c r="AK1" s="22" t="n"/>
+      <c r="AH1" s="23" t="n"/>
+      <c r="AI1" s="23" t="n"/>
+      <c r="AJ1" s="23" t="n"/>
+      <c r="AK1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n"/>
@@ -5940,61 +6070,61 @@
           <t>傾斜</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="n"/>
-      <c r="F2" s="22" t="n"/>
-      <c r="G2" s="20" t="n">
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="23" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
-      <c r="J2" s="22" t="n"/>
-      <c r="K2" s="20" t="n">
+      <c r="H2" s="23" t="n"/>
+      <c r="I2" s="23" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="21" t="n"/>
-      <c r="M2" s="21" t="n"/>
-      <c r="N2" s="22" t="n"/>
-      <c r="O2" s="20" t="n">
+      <c r="L2" s="23" t="n"/>
+      <c r="M2" s="23" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="21" t="n"/>
-      <c r="Q2" s="21" t="n"/>
-      <c r="R2" s="22" t="n"/>
-      <c r="S2" s="20" t="n">
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="21" t="n"/>
-      <c r="U2" s="21" t="n"/>
-      <c r="V2" s="22" t="n"/>
-      <c r="W2" s="20" t="n">
+      <c r="T2" s="23" t="n"/>
+      <c r="U2" s="23" t="n"/>
+      <c r="V2" s="21" t="n"/>
+      <c r="W2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="X2" s="21" t="n"/>
-      <c r="Y2" s="21" t="n"/>
-      <c r="Z2" s="22" t="n"/>
+      <c r="X2" s="23" t="n"/>
+      <c r="Y2" s="23" t="n"/>
+      <c r="Z2" s="21" t="n"/>
       <c r="AA2" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="AB2" s="22" t="n"/>
+      <c r="AB2" s="21" t="n"/>
       <c r="AC2" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="AD2" s="22" t="n"/>
+      <c r="AD2" s="21" t="n"/>
       <c r="AE2" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AF2" s="22" t="n"/>
-      <c r="AG2" s="20" t="n">
+      <c r="AF2" s="21" t="n"/>
+      <c r="AG2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" s="21" t="n"/>
-      <c r="AI2" s="21" t="n"/>
-      <c r="AJ2" s="22" t="n"/>
-      <c r="AK2" s="20" t="n">
+      <c r="AH2" s="23" t="n"/>
+      <c r="AI2" s="23" t="n"/>
+      <c r="AJ2" s="21" t="n"/>
+      <c r="AK2" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6190,42 +6320,42 @@
       <c r="B4" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6246,20 +6376,20 @@
       <c r="X4" s="1" t="n"/>
       <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
-      <c r="AA4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB4" s="22" t="n"/>
+      <c r="AA4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB4" s="21" t="n"/>
       <c r="AC4" s="1" t="n"/>
-      <c r="AD4" s="22" t="n"/>
-      <c r="AE4" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF4" s="22" t="n"/>
+      <c r="AD4" s="21" t="n"/>
+      <c r="AE4" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF4" s="21" t="n"/>
       <c r="AG4" s="1" t="n"/>
       <c r="AH4" s="1" t="n"/>
       <c r="AI4" s="1" t="n"/>
@@ -6271,42 +6401,42 @@
       <c r="B5" s="1" t="n">
         <v>3.9</v>
       </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6327,20 +6457,20 @@
       <c r="X5" s="1" t="n"/>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB5" s="22" t="n"/>
+      <c r="AA5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB5" s="21" t="n"/>
       <c r="AC5" s="1" t="n"/>
-      <c r="AD5" s="22" t="n"/>
-      <c r="AE5" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF5" s="22" t="n"/>
+      <c r="AD5" s="21" t="n"/>
+      <c r="AE5" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF5" s="21" t="n"/>
       <c r="AG5" s="1" t="n"/>
       <c r="AH5" s="1" t="n"/>
       <c r="AI5" s="1" t="n"/>
@@ -6352,42 +6482,42 @@
       <c r="B6" s="1" t="n">
         <v>3.8</v>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6408,20 +6538,20 @@
       <c r="X6" s="1" t="n"/>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
-      <c r="AA6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB6" s="22" t="n"/>
+      <c r="AA6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB6" s="21" t="n"/>
       <c r="AC6" s="1" t="n"/>
-      <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF6" s="22" t="n"/>
+      <c r="AD6" s="21" t="n"/>
+      <c r="AE6" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF6" s="21" t="n"/>
       <c r="AG6" s="1" t="n"/>
       <c r="AH6" s="1" t="n"/>
       <c r="AI6" s="1" t="n"/>
@@ -6437,62 +6567,62 @@
       <c r="D7" s="1" t="n"/>
       <c r="E7" s="1" t="n"/>
       <c r="F7" s="1" t="n"/>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="O7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R7" s="23" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R7" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6505,29 +6635,29 @@
       <c r="X7" s="1" t="n"/>
       <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
-      <c r="AA7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF7" s="22" t="n"/>
+      <c r="AA7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB7" s="21" t="n"/>
+      <c r="AC7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD7" s="21" t="n"/>
+      <c r="AE7" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF7" s="21" t="n"/>
       <c r="AG7" s="1" t="n"/>
       <c r="AH7" s="1" t="n"/>
       <c r="AI7" s="1" t="n"/>
       <c r="AJ7" s="1" t="n"/>
-      <c r="AK7" s="23" t="inlineStr">
+      <c r="AK7" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6542,62 +6672,62 @@
       <c r="D8" s="1" t="n"/>
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="n"/>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="M8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R8" s="23" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R8" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6610,29 +6740,29 @@
       <c r="X8" s="1" t="n"/>
       <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="1" t="n"/>
-      <c r="AA8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF8" s="22" t="n"/>
+      <c r="AA8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB8" s="21" t="n"/>
+      <c r="AC8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD8" s="21" t="n"/>
+      <c r="AE8" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF8" s="21" t="n"/>
       <c r="AG8" s="1" t="n"/>
       <c r="AH8" s="1" t="n"/>
       <c r="AI8" s="1" t="n"/>
       <c r="AJ8" s="1" t="n"/>
-      <c r="AK8" s="23" t="inlineStr">
+      <c r="AK8" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6651,62 +6781,62 @@
       <c r="D9" s="1" t="n"/>
       <c r="E9" s="1" t="n"/>
       <c r="F9" s="1" t="n"/>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="M9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="N9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="O9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R9" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6719,29 +6849,29 @@
       <c r="X9" s="1" t="n"/>
       <c r="Y9" s="1" t="n"/>
       <c r="Z9" s="1" t="n"/>
-      <c r="AA9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB9" s="22" t="n"/>
-      <c r="AC9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF9" s="22" t="n"/>
+      <c r="AA9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB9" s="21" t="n"/>
+      <c r="AC9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD9" s="21" t="n"/>
+      <c r="AE9" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF9" s="21" t="n"/>
       <c r="AG9" s="1" t="n"/>
       <c r="AH9" s="1" t="n"/>
       <c r="AI9" s="1" t="n"/>
       <c r="AJ9" s="1" t="n"/>
-      <c r="AK9" s="23" t="inlineStr">
+      <c r="AK9" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6756,62 +6886,62 @@
       <c r="D10" s="1" t="n"/>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="N10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R10" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6824,29 +6954,29 @@
       <c r="X10" s="1" t="n"/>
       <c r="Y10" s="1" t="n"/>
       <c r="Z10" s="1" t="n"/>
-      <c r="AA10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF10" s="22" t="n"/>
+      <c r="AA10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB10" s="21" t="n"/>
+      <c r="AC10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD10" s="21" t="n"/>
+      <c r="AE10" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF10" s="21" t="n"/>
       <c r="AG10" s="1" t="n"/>
       <c r="AH10" s="1" t="n"/>
       <c r="AI10" s="1" t="n"/>
       <c r="AJ10" s="1" t="n"/>
-      <c r="AK10" s="23" t="inlineStr">
+      <c r="AK10" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6861,62 +6991,62 @@
       <c r="D11" s="1" t="n"/>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="1" t="n"/>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="M11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="O11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R11" s="23" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R11" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6929,29 +7059,29 @@
       <c r="X11" s="1" t="n"/>
       <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="1" t="n"/>
-      <c r="AA11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB11" s="22" t="n"/>
-      <c r="AC11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD11" s="22" t="n"/>
-      <c r="AE11" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF11" s="22" t="n"/>
+      <c r="AA11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF11" s="21" t="n"/>
       <c r="AG11" s="1" t="n"/>
       <c r="AH11" s="1" t="n"/>
       <c r="AI11" s="1" t="n"/>
       <c r="AJ11" s="1" t="n"/>
-      <c r="AK11" s="23" t="inlineStr">
+      <c r="AK11" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -6974,80 +7104,80 @@
       <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
       <c r="N12" s="1" t="n"/>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="S12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="T12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="U12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="V12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="W12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y12" s="23" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="T12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="W12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y12" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z12" s="1" t="n"/>
-      <c r="AA12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB12" s="22" t="n"/>
-      <c r="AC12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD12" s="22" t="n"/>
-      <c r="AE12" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF12" s="22" t="n"/>
+      <c r="AA12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB12" s="21" t="n"/>
+      <c r="AC12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD12" s="21" t="n"/>
+      <c r="AE12" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF12" s="21" t="n"/>
       <c r="AG12" s="1" t="n"/>
       <c r="AH12" s="1" t="n"/>
       <c r="AI12" s="1" t="n"/>
@@ -7071,80 +7201,80 @@
       <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
       <c r="N13" s="1" t="n"/>
-      <c r="O13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="S13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="U13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="W13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y13" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="S13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="T13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="V13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="W13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y13" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z13" s="1" t="n"/>
-      <c r="AA13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB13" s="22" t="n"/>
-      <c r="AC13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD13" s="22" t="n"/>
-      <c r="AE13" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF13" s="22" t="n"/>
+      <c r="AA13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB13" s="21" t="n"/>
+      <c r="AC13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD13" s="21" t="n"/>
+      <c r="AE13" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF13" s="21" t="n"/>
       <c r="AG13" s="1" t="n"/>
       <c r="AH13" s="1" t="n"/>
       <c r="AI13" s="1" t="n"/>
@@ -7172,80 +7302,80 @@
       <c r="L14" s="1" t="n"/>
       <c r="M14" s="1" t="n"/>
       <c r="N14" s="1" t="n"/>
-      <c r="O14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="S14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="T14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="U14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="V14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="W14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y14" s="23" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="S14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="T14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="V14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="W14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y14" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z14" s="1" t="n"/>
-      <c r="AA14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB14" s="22" t="n"/>
-      <c r="AC14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD14" s="22" t="n"/>
-      <c r="AE14" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF14" s="22" t="n"/>
+      <c r="AA14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB14" s="21" t="n"/>
+      <c r="AC14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD14" s="21" t="n"/>
+      <c r="AE14" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF14" s="21" t="n"/>
       <c r="AG14" s="1" t="n"/>
       <c r="AH14" s="1" t="n"/>
       <c r="AI14" s="1" t="n"/>
@@ -7269,80 +7399,80 @@
       <c r="L15" s="1" t="n"/>
       <c r="M15" s="1" t="n"/>
       <c r="N15" s="1" t="n"/>
-      <c r="O15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="S15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="T15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="U15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="V15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="W15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y15" s="23" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="T15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="V15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="W15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y15" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z15" s="1" t="n"/>
-      <c r="AA15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD15" s="22" t="n"/>
-      <c r="AE15" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF15" s="22" t="n"/>
+      <c r="AA15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB15" s="21" t="n"/>
+      <c r="AC15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD15" s="21" t="n"/>
+      <c r="AE15" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF15" s="21" t="n"/>
       <c r="AG15" s="1" t="n"/>
       <c r="AH15" s="1" t="n"/>
       <c r="AI15" s="1" t="n"/>
@@ -7366,80 +7496,80 @@
       <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
       <c r="N16" s="1" t="n"/>
-      <c r="O16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="S16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="T16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="U16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="V16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="W16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y16" s="23" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="R16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="T16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="V16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="W16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y16" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z16" s="1" t="n"/>
-      <c r="AA16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AB16" s="22" t="n"/>
-      <c r="AC16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD16" s="22" t="n"/>
-      <c r="AE16" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF16" s="22" t="n"/>
+      <c r="AA16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AB16" s="21" t="n"/>
+      <c r="AC16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD16" s="21" t="n"/>
+      <c r="AE16" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF16" s="21" t="n"/>
       <c r="AG16" s="1" t="n"/>
       <c r="AH16" s="1" t="n"/>
       <c r="AI16" s="1" t="n"/>
@@ -7471,17 +7601,17 @@
       <c r="T17" s="1" t="n"/>
       <c r="U17" s="1" t="n"/>
       <c r="V17" s="1" t="n"/>
-      <c r="W17" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X17" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y17" s="23" t="inlineStr">
+      <c r="W17" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X17" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y17" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7489,27 +7619,27 @@
       <c r="Z17" s="1" t="n"/>
       <c r="AA17" s="1" t="n"/>
       <c r="AB17" s="1" t="n"/>
-      <c r="AC17" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD17" s="22" t="n"/>
-      <c r="AE17" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF17" s="22" t="n"/>
-      <c r="AG17" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AH17" s="22" t="n"/>
+      <c r="AC17" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD17" s="21" t="n"/>
+      <c r="AE17" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF17" s="21" t="n"/>
+      <c r="AG17" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AH17" s="21" t="n"/>
       <c r="AI17" s="1" t="n"/>
       <c r="AJ17" s="1" t="n"/>
-      <c r="AK17" s="23" t="inlineStr">
+      <c r="AK17" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7540,17 +7670,17 @@
       <c r="T18" s="1" t="n"/>
       <c r="U18" s="1" t="n"/>
       <c r="V18" s="1" t="n"/>
-      <c r="W18" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X18" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y18" s="23" t="inlineStr">
+      <c r="W18" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X18" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y18" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7558,27 +7688,27 @@
       <c r="Z18" s="1" t="n"/>
       <c r="AA18" s="1" t="n"/>
       <c r="AB18" s="1" t="n"/>
-      <c r="AC18" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AH18" s="22" t="n"/>
+      <c r="AC18" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD18" s="21" t="n"/>
+      <c r="AE18" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF18" s="21" t="n"/>
+      <c r="AG18" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AH18" s="21" t="n"/>
       <c r="AI18" s="1" t="n"/>
       <c r="AJ18" s="1" t="n"/>
-      <c r="AK18" s="23" t="inlineStr">
+      <c r="AK18" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7613,17 +7743,17 @@
       <c r="T19" s="1" t="n"/>
       <c r="U19" s="1" t="n"/>
       <c r="V19" s="1" t="n"/>
-      <c r="W19" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="X19" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Y19" s="23" t="inlineStr">
+      <c r="W19" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="X19" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Y19" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7631,27 +7761,27 @@
       <c r="Z19" s="1" t="n"/>
       <c r="AA19" s="1" t="n"/>
       <c r="AB19" s="1" t="n"/>
-      <c r="AC19" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="23" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="AH19" s="22" t="n"/>
+      <c r="AC19" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AD19" s="21" t="n"/>
+      <c r="AE19" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AF19" s="21" t="n"/>
+      <c r="AG19" s="20" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="AH19" s="21" t="n"/>
       <c r="AI19" s="1" t="n"/>
       <c r="AJ19" s="1" t="n"/>
-      <c r="AK19" s="23" t="inlineStr">
+      <c r="AK19" s="20" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
@@ -7674,12 +7804,12 @@
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="AC13:AD13"/>
     <mergeCell ref="G1:J1"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AA9:AB9"/>
     <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="AC18:AD18"/>
     <mergeCell ref="AE18:AF18"/>
     <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="S1:V1"/>
     <mergeCell ref="AA15:AB15"/>
     <mergeCell ref="AC15:AD15"/>
     <mergeCell ref="AA6:AB6"/>
@@ -7692,9 +7822,9 @@
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AE8:AF8"/>
     <mergeCell ref="AE17:AF17"/>
-    <mergeCell ref="AA14:AB14"/>
     <mergeCell ref="AG17:AH17"/>
     <mergeCell ref="AA7:AB7"/>
+    <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="AA16:AB16"/>
     <mergeCell ref="AC10:AD10"/>
     <mergeCell ref="S2:V2"/>
@@ -7723,7 +7853,7 @@
     <mergeCell ref="AE11:AF11"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA14:AB14"/>
     <mergeCell ref="AE4:AF4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomok\OneDrive\デスクトップ\WebAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E8FE1E-7BAE-46E8-A1BD-DDD9CC56C452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABC27B9-AA86-4B3B-A9AF-03D170DBB115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="183">
   <si>
     <t>参加</t>
   </si>
@@ -573,6 +573,10 @@
   </si>
   <si>
     <t>指</t>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -794,14 +798,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1961,18 +1965,20 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
@@ -1982,10 +1988,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
         <v>3.5</v>
@@ -1993,9 +1999,7 @@
       <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
         <v>29</v>
       </c>
@@ -2005,12 +2009,12 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="6">
         <v>3.5</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -2026,12 +2030,12 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>3.5</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -2047,10 +2051,10 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="3">
         <v>3.5</v>
@@ -2064,11 +2068,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
+      <c r="A10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -2079,30 +2083,30 @@
       <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>21</v>
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="6">
         <v>3.5</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="F11"/>
       <c r="G11" s="3" t="s">
         <v>29</v>
       </c>
@@ -2112,10 +2116,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6">
         <v>3.5</v>
@@ -2133,10 +2137,10 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6">
         <v>3.5</v>
@@ -2154,18 +2158,18 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="6">
-        <v>3.5</v>
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F14"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
         <v>29</v>
       </c>
@@ -2175,34 +2179,34 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="3">
-        <v>3.5</v>
+      <c r="D15" s="6">
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15"/>
       <c r="G15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="3">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D16" s="6">
+        <v>3.5</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
@@ -2213,22 +2217,20 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A17" s="3"/>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="6">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F17"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
         <v>29</v>
       </c>
@@ -2236,13 +2238,13 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="3"/>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>29</v>
@@ -2255,7 +2257,7 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="3"/>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>14</v>
@@ -2274,24 +2276,26 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="3"/>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D20" s="3">
         <v>4</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="3"/>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>11</v>
@@ -2299,18 +2303,16 @@
       <c r="D21" s="3">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="3"/>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
@@ -2321,9 +2323,7 @@
       <c r="E22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>29</v>
       </c>
@@ -2331,10 +2331,10 @@
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="3"/>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>4</v>
@@ -2352,12 +2352,12 @@
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="3"/>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="6">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3">
         <v>4</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -2373,7 +2373,7 @@
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="3"/>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>11</v>
@@ -2394,7 +2394,7 @@
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="3"/>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>11</v>
@@ -2415,7 +2415,7 @@
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="3"/>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>11</v>
@@ -2436,7 +2436,7 @@
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="3"/>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
@@ -2447,7 +2447,9 @@
       <c r="E28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F28"/>
+      <c r="F28" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>29</v>
       </c>
@@ -2455,28 +2457,26 @@
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="3"/>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="6">
         <v>4</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="F29"/>
       <c r="G29" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="3"/>
-      <c r="B30" s="18" t="s">
-        <v>53</v>
+      <c r="B30" t="s">
+        <v>52</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>11</v>
@@ -2487,18 +2487,20 @@
       <c r="E30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G30" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="3"/>
-      <c r="B31" t="s">
-        <v>54</v>
+      <c r="B31" s="18" t="s">
+        <v>53</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D31" s="3">
         <v>4</v>
@@ -2514,7 +2516,7 @@
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="3"/>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>14</v>
@@ -2533,10 +2535,10 @@
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="3"/>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D33" s="3">
         <v>4</v>
@@ -2552,18 +2554,18 @@
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="3"/>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="3">
         <v>4</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F34"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2573,7 @@
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="3"/>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>11</v>
@@ -2582,7 +2584,7 @@
       <c r="E35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35"/>
       <c r="G35" s="3" t="s">
         <v>29</v>
       </c>
@@ -5002,117 +5004,117 @@
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="23" t="s">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="23" t="s">
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="23" t="s">
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="23" t="s">
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="23"/>
       <c r="AA1" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="23" t="s">
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="AH1" s="24"/>
-      <c r="AI1" s="24"/>
-      <c r="AJ1" s="24"/>
-      <c r="AK1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="23"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" s="13"/>
       <c r="B2" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="21">
         <v>0</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="21">
         <v>1</v>
       </c>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="23">
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="21">
         <v>0</v>
       </c>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="23">
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="21">
         <v>1</v>
       </c>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="23">
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="21">
         <v>0</v>
       </c>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="23">
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="21">
         <v>1</v>
       </c>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="23"/>
       <c r="AA2" s="25">
         <v>4</v>
       </c>
-      <c r="AB2" s="22"/>
+      <c r="AB2" s="23"/>
       <c r="AC2" s="25">
         <v>4</v>
       </c>
-      <c r="AD2" s="22"/>
+      <c r="AD2" s="23"/>
       <c r="AE2" s="25">
         <v>8</v>
       </c>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="23">
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="21">
         <v>0</v>
       </c>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="23"/>
       <c r="AK2" s="14">
         <v>1</v>
       </c>
@@ -5275,16 +5277,16 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB4" s="22"/>
+      <c r="AA4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="23"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="15"/>
-      <c r="AE4" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF4" s="22"/>
+      <c r="AE4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="23"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
@@ -5336,16 +5338,16 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB5" s="22"/>
+      <c r="AA5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="23"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="15"/>
-      <c r="AE5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF5" s="22"/>
+      <c r="AE5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="23"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -5397,16 +5399,16 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB6" s="22"/>
+      <c r="AA6" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB6" s="23"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="15"/>
-      <c r="AE6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF6" s="22"/>
+      <c r="AE6" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF6" s="23"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -5466,18 +5468,18 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF7" s="22"/>
+      <c r="AA7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF7" s="23"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -5539,18 +5541,18 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF8" s="22"/>
+      <c r="AA8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF8" s="23"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -5614,18 +5616,18 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF9" s="22"/>
+      <c r="AA9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF9" s="23"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -5687,18 +5689,18 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF10" s="22"/>
+      <c r="AA10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD10" s="23"/>
+      <c r="AE10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF10" s="23"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
@@ -5760,18 +5762,18 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF11" s="22"/>
+      <c r="AA11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD11" s="23"/>
+      <c r="AE11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF11" s="23"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -5831,18 +5833,18 @@
         <v>29</v>
       </c>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF12" s="22"/>
+      <c r="AA12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF12" s="23"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
@@ -5900,18 +5902,18 @@
         <v>29</v>
       </c>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF13" s="22"/>
+      <c r="AA13" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD13" s="23"/>
+      <c r="AE13" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF13" s="23"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -5971,18 +5973,18 @@
         <v>29</v>
       </c>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF14" s="22"/>
+      <c r="AA14" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF14" s="23"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
@@ -6040,18 +6042,18 @@
         <v>29</v>
       </c>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF15" s="22"/>
+      <c r="AA15" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF15" s="23"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
@@ -6109,18 +6111,18 @@
         <v>29</v>
       </c>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF16" s="22"/>
+      <c r="AA16" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF16" s="23"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
@@ -6164,18 +6166,18 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH17" s="22"/>
+      <c r="AC17" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF17" s="23"/>
+      <c r="AG17" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH17" s="23"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="11" t="s">
@@ -6219,18 +6221,18 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH18" s="22"/>
+      <c r="AC18" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF18" s="23"/>
+      <c r="AG18" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH18" s="23"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="11" t="s">
@@ -6276,18 +6278,18 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH19" s="22"/>
+      <c r="AC19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD19" s="23"/>
+      <c r="AE19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF19" s="23"/>
+      <c r="AG19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH19" s="23"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="11" t="s">
@@ -6299,11 +6301,37 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AD15"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="AC8:AD8"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="AE13:AF13"/>
@@ -6320,6 +6348,11 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="AA7:AB7"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="AA16:AB16"/>
@@ -6328,40 +6361,9 @@
     <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="AC11:AD11"/>
     <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE18:AF18"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AD15"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="AC8:AD8"/>
     <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="W2:Z2"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AE8:AF8"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE5:AF5"/>
     <mergeCell ref="AC17:AD17"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AE17:AF17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
